--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -613,7 +613,11 @@
       <c r="T2" t="n">
         <v>-45</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -689,7 +693,11 @@
       <c r="T3" t="n">
         <v>-47</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -831,7 +839,11 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -897,7 +909,11 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -963,7 +979,11 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -1029,7 +1049,11 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -1095,7 +1119,11 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>蝦皮</t>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -613,11 +613,7 @@
       <c r="T2" t="n">
         <v>-45</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>未匹配</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>蝦皮</t>
@@ -693,11 +689,7 @@
       <c r="T3" t="n">
         <v>-47</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>未匹配</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>蝦皮</t>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +541,690 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26020345883124</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L], 莫代爾長袖打底上衣[【圓領】白色L], 素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L(1); HFA02001-CN-WH-L(1); HFE03001-WH-L(1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>144</v>
+      </c>
+      <c r="S2" t="n">
+        <v>178</v>
+      </c>
+      <c r="T2" t="n">
+        <v>174</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26020746340576</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL], 超薄裸感冰絲男士四角內褲[咖啡色XL], 超薄裸感冰絲男士四角內褲[酒紅色XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[紫色XL], 超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL(1); HME03001-BR-XL(1); HME03001-RD-XL(1); HME03001-DN-XL(1); HME03001-PU-XL(1); HME03001-GY-XL(1); HME03001-WH-XL(3)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>603</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>347</v>
+      </c>
+      <c r="T3" t="n">
+        <v>256</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26020946668756</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L], 超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L], 超薄裸感冰絲男士四角內褲[白色L], 超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(1); HME03001-DN-L(1); HME03001-BK-L(1); HME03001-WH-L(1); HME03001-BR-L(1)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>335</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>161</v>
+      </c>
+      <c r="S4" t="n">
+        <v>192</v>
+      </c>
+      <c r="T4" t="n">
+        <v>143</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26022147703801</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M], 超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[灰色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M(1); HME03001-BK-M(3); HME03001-GY-M(3); HME03001-DN-M(3)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>670</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>322</v>
+      </c>
+      <c r="S5" t="n">
+        <v>385</v>
+      </c>
+      <c r="T5" t="n">
+        <v>285</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26022147748383</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L(4)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>130</v>
+      </c>
+      <c r="S6" t="n">
+        <v>156</v>
+      </c>
+      <c r="T6" t="n">
+        <v>112</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26022347876463</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(4)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>268</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>128</v>
+      </c>
+      <c r="S7" t="n">
+        <v>154</v>
+      </c>
+      <c r="T7" t="n">
+        <v>114</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26022448136964</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M(5)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>335</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>162</v>
+      </c>
+      <c r="S8" t="n">
+        <v>195</v>
+      </c>
+      <c r="T8" t="n">
+        <v>140</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26022648266686</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶中長版 ❗️微透❗️::L], 夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶加長版 ❗️微透❗️::L]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>268</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>241</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26022648358294</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L(1); HME03001-BK-L(1)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>134</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>65</v>
+      </c>
+      <c r="S10" t="n">
+        <v>78</v>
+      </c>
+      <c r="T10" t="n">
+        <v>56</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>露天</t>
         </is>
       </c>
     </row>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -548,10 +548,8 @@
       <c r="A2" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>26020345883124</t>
-        </is>
+      <c r="B2" t="n">
+        <v>26020345883124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -624,10 +622,8 @@
       <c r="A3" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26020746340576</t>
-        </is>
+      <c r="B3" t="n">
+        <v>26020746340576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -657,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>
@@ -700,10 +696,8 @@
       <c r="A4" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>26020946668756</t>
-        </is>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -776,10 +770,8 @@
       <c r="A5" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>26022147703801</t>
-        </is>
+      <c r="B5" t="n">
+        <v>26022147703801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -852,10 +844,8 @@
       <c r="A6" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>26022147748383</t>
-        </is>
+      <c r="B6" t="n">
+        <v>26022147748383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -928,10 +918,8 @@
       <c r="A7" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>26022347876463</t>
-        </is>
+      <c r="B7" t="n">
+        <v>26022347876463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1004,10 +992,8 @@
       <c r="A8" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>26022448136964</t>
-        </is>
+      <c r="B8" t="n">
+        <v>26022448136964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1080,10 +1066,8 @@
       <c r="A9" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>26022648266686</t>
-        </is>
+      <c r="B9" t="n">
+        <v>26022648266686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1156,10 +1140,8 @@
       <c r="A10" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>26022648358294</t>
-        </is>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="T2" t="n">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="T2" t="n">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -606,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="T2" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -582,10 +582,10 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -606,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="T2" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -582,7 +582,7 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,6 +1210,1344 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>25062521046189.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>未取貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S(5)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-60</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>260101UQC2FXC5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>退貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色M], 莫代爾打底連身裙[吊帶款/短版/白色M]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-M(1); HFC01001-TS-SH-WH-M(1)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-45</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>260101VGTQ5TTD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>退貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL(1)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>102</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-27</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>260111RDUTKB7X</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>退貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G(1)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>99</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>103</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26020345883124.0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L], 莫代爾長袖打底上衣[【圓領】白色L], 素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L(1); HFA02001-CN-WH-L(1); HFE03001-WH-L(1)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>352</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>18</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>144</v>
+      </c>
+      <c r="S15" t="n">
+        <v>178</v>
+      </c>
+      <c r="T15" t="n">
+        <v>174</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>26020746340576.0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL], 超薄裸感冰絲男士四角內褲[咖啡色XL], 超薄裸感冰絲男士四角內褲[酒紅色XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[紫色XL], 超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL(1); HME03001-BR-XL(1); HME03001-RD-XL(1); HME03001-DN-XL(1); HME03001-PU-XL(1); HME03001-GY-XL(1); HME03001-WH-XL(3)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>603</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>65</v>
+      </c>
+      <c r="K16" t="n">
+        <v>35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>290</v>
+      </c>
+      <c r="S16" t="n">
+        <v>347</v>
+      </c>
+      <c r="T16" t="n">
+        <v>256</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26020946668756.0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L], 超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L], 超薄裸感冰絲男士四角內褲[白色L], 超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(1); HME03001-DN-L(1); HME03001-BK-L(1); HME03001-WH-L(1); HME03001-BR-L(1)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>335</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>65</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>161</v>
+      </c>
+      <c r="S17" t="n">
+        <v>192</v>
+      </c>
+      <c r="T17" t="n">
+        <v>143</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26022147703801.0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M], 超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[灰色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M(1); HME03001-BK-M(3); HME03001-GY-M(3); HME03001-DN-M(3)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>670</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>33</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>322</v>
+      </c>
+      <c r="S18" t="n">
+        <v>385</v>
+      </c>
+      <c r="T18" t="n">
+        <v>285</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26022147748383.0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L(4)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>268</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>130</v>
+      </c>
+      <c r="S19" t="n">
+        <v>156</v>
+      </c>
+      <c r="T19" t="n">
+        <v>112</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26022347876463.0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(4)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>268</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>128</v>
+      </c>
+      <c r="S20" t="n">
+        <v>154</v>
+      </c>
+      <c r="T20" t="n">
+        <v>114</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>26022448136964.0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M(5)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>335</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>55</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>50</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="n">
+        <v>17</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>162</v>
+      </c>
+      <c r="S21" t="n">
+        <v>195</v>
+      </c>
+      <c r="T21" t="n">
+        <v>140</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>26022648266686.0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶中長版 ❗️微透❗️::L], 夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶加長版 ❗️微透❗️::L]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>268</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>55</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>50</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>27</v>
+      </c>
+      <c r="T22" t="n">
+        <v>241</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>26022648358294.0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L(1); HME03001-BK-L(1)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>134</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>56</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.260101T9JAVCHM：未取貨</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.260101U289VMH1：出貨前取消訂單</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3.260101UQC2FXC5：整單退貨</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4.260101VGTQ5TTD：部份退貨</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5.260111RDUTKB7X：部份退貨</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2548,6 +2548,82 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#144485</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>未取貨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M(1)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>65</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>65</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>65</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-65</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2624,6 +2624,1070 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45804</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#125786</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L], 遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿[黑色, M], 遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿[象牙淺灰, S]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-L(3); HFB01001-BK-M(1); HFB01001-GY-S(1)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>954</v>
+      </c>
+      <c r="G30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>138</v>
+      </c>
+      <c r="S30" t="n">
+        <v>188</v>
+      </c>
+      <c r="T30" t="n">
+        <v>766</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>#140265</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑], 單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物], 單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味], 單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂花], 單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗], 單顆入.ᐟ台灣手工黑糖塊[【單顆18G】海燕窩]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG(10); YGJ03002-RFH(10); YGJ03002-OR(10); YGJ03002-OS(10); YGJ03002-RDL(10); YGJ03002-SBN(10)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>540</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="n">
+        <v>65</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>65</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>180</v>
+      </c>
+      <c r="S31" t="n">
+        <v>240</v>
+      </c>
+      <c r="T31" t="n">
+        <v>300</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#143171</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HME03001-BK-XL(30)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G32" t="n">
+        <v>180</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>973</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1153</v>
+      </c>
+      <c r="T32" t="n">
+        <v>797</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#149034</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L], 柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-L(1); HME03002-SO-BK-L(1)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>144</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>65</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>65</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>92</v>
+      </c>
+      <c r="S33" t="n">
+        <v>92</v>
+      </c>
+      <c r="T33" t="n">
+        <v>52</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#149099</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[咖啡色XL], 超薄裸感冰絲男士四角內褲[黑色XL], IKEA 正版環保購物袋[【手提款】71L]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HGA02001-DGY-XL(1); HME03001-DN-XL(3); HME03001-GY-XL(3); HME03001-BR-XL(3); HME03001-BK-XL(1); HGI03002-HT(1)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>989</v>
+      </c>
+      <c r="G34" t="n">
+        <v>110</v>
+      </c>
+      <c r="H34" t="n">
+        <v>65</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>65</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>494</v>
+      </c>
+      <c r="S34" t="n">
+        <v>604</v>
+      </c>
+      <c r="T34" t="n">
+        <v>385</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>#149309</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL], 柔順莫代爾男士四角內褲[【條紋】淺藍色XL], 柔順莫代爾男士四角內褲[【條紋】深藍色XL], 柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL(1); HME03002-ST-LB-XL(1); HME03002-ST-DN-XL(1); HME03002-SO-DN-XL(1)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>288</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>65</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>65</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>183</v>
+      </c>
+      <c r="S35" t="n">
+        <v>188</v>
+      </c>
+      <c r="T35" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#150109</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL(10)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>720</v>
+      </c>
+      <c r="G36" t="n">
+        <v>60</v>
+      </c>
+      <c r="H36" t="n">
+        <v>65</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>65</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>459</v>
+      </c>
+      <c r="S36" t="n">
+        <v>519</v>
+      </c>
+      <c r="T36" t="n">
+        <v>201</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#150161</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M], 舒適寬邊莫代爾女士三角內褲[紫羅蘭M], 舒適寬邊莫代爾女士三角內褲[煙粉色M], 舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M(2); HFE03002-PU-M(2); HFE03002-PK-M(2); HFE03002-BG-M(2)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>65</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>65</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>308</v>
+      </c>
+      <c r="S37" t="n">
+        <v>308</v>
+      </c>
+      <c r="T37" t="n">
+        <v>292</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>#150323</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色M], 超薄裸感冰絲男士四角內褲[灰色M], 超薄裸感冰絲男士四角內褲[酒紅色M], 超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HME03001-WH-M(3); HME03001-GY-M(3); HME03001-RD-M(2); HME03001-BK-M(5); HME03001-DN-M(4)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1105</v>
+      </c>
+      <c r="G38" t="n">
+        <v>176</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>65</v>
+      </c>
+      <c r="K38" t="n">
+        <v>65</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>547</v>
+      </c>
+      <c r="S38" t="n">
+        <v>723</v>
+      </c>
+      <c r="T38" t="n">
+        <v>382</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>#150475</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L], 超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L(10); HME03001-WH-L(10)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G39" t="n">
+        <v>120</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>65</v>
+      </c>
+      <c r="K39" t="n">
+        <v>65</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>644</v>
+      </c>
+      <c r="S39" t="n">
+        <v>764</v>
+      </c>
+      <c r="T39" t="n">
+        <v>536</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>#151671</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[酒紅色XL], 超薄裸感冰絲男士四角內褲[黑色XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[紫色XL]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL(2); HME03001-RD-XL(2); HME03001-BK-XL(2); HME03001-DN-XL(2); HME03001-PU-XL(2)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>650</v>
+      </c>
+      <c r="G40" t="n">
+        <v>60</v>
+      </c>
+      <c r="H40" t="n">
+        <v>65</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>65</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>323</v>
+      </c>
+      <c r="S40" t="n">
+        <v>383</v>
+      </c>
+      <c r="T40" t="n">
+        <v>267</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#151781</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>莫代爾男士柔感內衣[白色L]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HME03003-WH-L(1)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>165</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>65</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>65</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>95</v>
+      </c>
+      <c r="S41" t="n">
+        <v>95</v>
+      </c>
+      <c r="T41" t="n">
+        <v>70</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#152962</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL], 舒適寬邊莫代爾女士三角內褲[米咖色XL], 舒適寬邊莫代爾女士三角內褲[紫羅蘭XL], 舒適寬邊莫代爾女士三角內褲[黑色XL], 舒適寬邊莫代爾女士三角內褲[煙粉色XL], 舒適寬邊莫代爾女士三角內褲[摩卡色XL], 素色冰絲女士三角內褲[丁香紫XL], 素色冰絲女士三角內褲[中豆紅XL], 素色冰絲女士三角內褲[膚色XL], 素色冰絲女士三角內褲[藍灰色XL], 素色冰絲女士三角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-XL(1); HFE03002-BG-XL(1); HFE03002-PU-XL(1); HFE03002-BK-XL(1); HFE03002-PK-XL(1); HFE03002-BR-XL(1); HFE03001-PU-XL(1); HFE03001-RD-XL(2); HFE03001-SK-XL(1); HFE03001-BU-XL(1); HFE03001-BK-XL(1)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>744</v>
+      </c>
+      <c r="G42" t="n">
+        <v>45</v>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>65</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>361</v>
+      </c>
+      <c r="S42" t="n">
+        <v>406</v>
+      </c>
+      <c r="T42" t="n">
+        <v>338</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#152968</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M(4); HME03001-DN-M(4)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>520</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>65</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>65</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>258</v>
+      </c>
+      <c r="S43" t="n">
+        <v>258</v>
+      </c>
+      <c r="T43" t="n">
+        <v>262</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3688,6 +3688,162 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45175</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#68442</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲[升級版🆙煙粉色, XL], 超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲[白色, XL], 超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲[丁香紫, XL]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>F(3); F(4); F(3)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>481</v>
+      </c>
+      <c r="G44" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" t="n">
+        <v>65</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>65</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>30</v>
+      </c>
+      <c r="T44" t="n">
+        <v>451</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#144712</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>退貨</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-WH-M(2)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>65</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>65</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>115</v>
+      </c>
+      <c r="T45" t="n">
+        <v>-115</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -548,8 +548,10 @@
       <c r="A2" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="B2" t="n">
-        <v>26020345883124</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26020345883124</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -611,7 +613,12 @@
       <c r="T2" t="n">
         <v>174</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.
+2.</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>露天</t>
@@ -622,8 +629,10 @@
       <c r="A3" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B3" t="n">
-        <v>26020746340576</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26020746340576</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -696,8 +705,10 @@
       <c r="A4" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B4" t="n">
-        <v>26020946668756</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26020946668756</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -770,8 +781,10 @@
       <c r="A5" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B5" t="n">
-        <v>26022147703801</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26022147703801</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -844,8 +857,10 @@
       <c r="A6" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B6" t="n">
-        <v>26022147748383</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26022147748383</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -918,8 +933,10 @@
       <c r="A7" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="B7" t="n">
-        <v>26022347876463</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26022347876463</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -992,8 +1009,10 @@
       <c r="A8" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B8" t="n">
-        <v>26022448136964</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26022448136964</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1066,8 +1085,10 @@
       <c r="A9" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B9" t="n">
-        <v>26022648266686</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26022648266686</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1140,8 +1161,10 @@
       <c r="A10" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B10" t="n">
-        <v>26022648358294</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26022648358294</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +541,690 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26020345883124</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L], 莫代爾長袖打底上衣[【圓領】白色L], 素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L(1); HFA02001-CN-WH-L(1); HFE03001-WH-L(1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>144</v>
+      </c>
+      <c r="S2" t="n">
+        <v>178</v>
+      </c>
+      <c r="T2" t="n">
+        <v>174</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26020746340576</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL], 超薄裸感冰絲男士四角內褲[咖啡色XL], 超薄裸感冰絲男士四角內褲[酒紅色XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[紫色XL], 超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL(1); HME03001-BR-XL(1); HME03001-RD-XL(1); HME03001-DN-XL(1); HME03001-PU-XL(1); HME03001-GY-XL(1); HME03001-WH-XL(3)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>603</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>382</v>
+      </c>
+      <c r="T3" t="n">
+        <v>221</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26020946668756</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L], 超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L], 超薄裸感冰絲男士四角內褲[白色L], 超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(1); HME03001-DN-L(1); HME03001-BK-L(1); HME03001-WH-L(1); HME03001-BR-L(1)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>335</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>161</v>
+      </c>
+      <c r="S4" t="n">
+        <v>197</v>
+      </c>
+      <c r="T4" t="n">
+        <v>138</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26022147703801</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M], 超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[灰色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M(1); HME03001-BK-M(3); HME03001-GY-M(3); HME03001-DN-M(3)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>670</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>322</v>
+      </c>
+      <c r="S5" t="n">
+        <v>385</v>
+      </c>
+      <c r="T5" t="n">
+        <v>285</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26022147748383</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L(4)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>130</v>
+      </c>
+      <c r="S6" t="n">
+        <v>161</v>
+      </c>
+      <c r="T6" t="n">
+        <v>107</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26022347876463</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(4)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>268</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>128</v>
+      </c>
+      <c r="S7" t="n">
+        <v>159</v>
+      </c>
+      <c r="T7" t="n">
+        <v>109</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26022448136964</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M(5)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>335</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>162</v>
+      </c>
+      <c r="S8" t="n">
+        <v>200</v>
+      </c>
+      <c r="T8" t="n">
+        <v>135</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26022648266686</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶中長版 ❗️微透❗️::L], 夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶加長版 ❗️微透❗️::L]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>268</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>32</v>
+      </c>
+      <c r="T9" t="n">
+        <v>236</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26022648358294</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L(1); HME03001-BK-L(1)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>134</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>65</v>
+      </c>
+      <c r="S10" t="n">
+        <v>83</v>
+      </c>
+      <c r="T10" t="n">
+        <v>51</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>露天</t>
         </is>
       </c>
     </row>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -548,10 +548,8 @@
       <c r="A2" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>26020345883124</t>
-        </is>
+      <c r="B2" t="n">
+        <v>26020345883124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -584,7 +582,7 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -608,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="T2" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -624,10 +622,8 @@
       <c r="A3" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26020746340576</t>
-        </is>
+      <c r="B3" t="n">
+        <v>26020746340576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -660,7 +656,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -684,10 +680,10 @@
         <v>290</v>
       </c>
       <c r="S3" t="n">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="T3" t="n">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
@@ -700,10 +696,8 @@
       <c r="A4" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>26020946668756</t>
-        </is>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -736,7 +730,7 @@
         <v>60</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -760,10 +754,10 @@
         <v>161</v>
       </c>
       <c r="S4" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="T4" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -776,10 +770,8 @@
       <c r="A5" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>26022147703801</t>
-        </is>
+      <c r="B5" t="n">
+        <v>26022147703801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -812,7 +804,7 @@
         <v>60</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -836,10 +828,10 @@
         <v>322</v>
       </c>
       <c r="S5" t="n">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="T5" t="n">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -852,10 +844,8 @@
       <c r="A6" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>26022147748383</t>
-        </is>
+      <c r="B6" t="n">
+        <v>26022147748383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -888,7 +878,7 @@
         <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -912,10 +902,10 @@
         <v>130</v>
       </c>
       <c r="S6" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="T6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
@@ -928,10 +918,8 @@
       <c r="A7" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>26022347876463</t>
-        </is>
+      <c r="B7" t="n">
+        <v>26022347876463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -964,7 +952,7 @@
         <v>60</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -988,10 +976,10 @@
         <v>128</v>
       </c>
       <c r="S7" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T7" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
@@ -1004,10 +992,8 @@
       <c r="A8" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>26022448136964</t>
-        </is>
+      <c r="B8" t="n">
+        <v>26022448136964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1040,7 +1026,7 @@
         <v>50</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1064,10 +1050,10 @@
         <v>162</v>
       </c>
       <c r="S8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="T8" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -1080,10 +1066,8 @@
       <c r="A9" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>26022648266686</t>
-        </is>
+      <c r="B9" t="n">
+        <v>26022648266686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1112,7 +1096,7 @@
         <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1136,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1156,10 +1140,8 @@
       <c r="A10" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>26022648358294</t>
-        </is>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1192,7 +1174,7 @@
         <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1216,10 +1198,10 @@
         <v>65</v>
       </c>
       <c r="S10" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="T10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +541,690 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26020345883124</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L], 莫代爾長袖打底上衣[【圓領】白色L], 素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L(1); HFA02001-CN-WH-L(1); HFE03001-WH-L(1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>144</v>
+      </c>
+      <c r="S2" t="n">
+        <v>178</v>
+      </c>
+      <c r="T2" t="n">
+        <v>174</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26020746340576</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL], 超薄裸感冰絲男士四角內褲[咖啡色XL], 超薄裸感冰絲男士四角內褲[酒紅色XL], 超薄裸感冰絲男士四角內褲[藏藍色XL], 超薄裸感冰絲男士四角內褲[紫色XL], 超薄裸感冰絲男士四角內褲[灰色XL], 超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL(1); HME03001-BR-XL(1); HME03001-RD-XL(1); HME03001-DN-XL(1); HME03001-PU-XL(1); HME03001-GY-XL(1); HME03001-WH-XL(3)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>603</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>312</v>
+      </c>
+      <c r="T3" t="n">
+        <v>291</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26020946668756</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L], 超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L], 超薄裸感冰絲男士四角內褲[白色L], 超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(1); HME03001-DN-L(1); HME03001-BK-L(1); HME03001-WH-L(1); HME03001-BR-L(1)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>335</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>161</v>
+      </c>
+      <c r="S4" t="n">
+        <v>187</v>
+      </c>
+      <c r="T4" t="n">
+        <v>148</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26022147703801</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M], 超薄裸感冰絲男士四角內褲[黑色M], 超薄裸感冰絲男士四角內褲[灰色M], 超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M(1); HME03001-BK-M(3); HME03001-GY-M(3); HME03001-DN-M(3)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>670</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>322</v>
+      </c>
+      <c r="S5" t="n">
+        <v>385</v>
+      </c>
+      <c r="T5" t="n">
+        <v>285</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26022147748383</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L(4)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>130</v>
+      </c>
+      <c r="S6" t="n">
+        <v>151</v>
+      </c>
+      <c r="T6" t="n">
+        <v>117</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26022347876463</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L(4)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>268</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>128</v>
+      </c>
+      <c r="S7" t="n">
+        <v>149</v>
+      </c>
+      <c r="T7" t="n">
+        <v>119</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26022448136964</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M(5)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>335</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>162</v>
+      </c>
+      <c r="S8" t="n">
+        <v>190</v>
+      </c>
+      <c r="T8" t="n">
+        <v>145</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26022648266686</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶中長版 ❗️微透❗️::L], 夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨[【白色】吊帶款▶加長版 ❗️微透❗️::L]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>268</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>246</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26022648358294</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L], 超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L(1); HME03001-BK-L(1)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>134</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>65</v>
+      </c>
+      <c r="S10" t="n">
+        <v>73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>61</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>露天</t>
         </is>
       </c>
     </row>

--- a/data/日報表.xlsx
+++ b/data/日報表.xlsx
@@ -548,10 +548,8 @@
       <c r="A2" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>26020345883124</t>
-        </is>
+      <c r="B2" t="n">
+        <v>26020345883124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -584,7 +582,7 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -608,10 +606,10 @@
         <v>144</v>
       </c>
       <c r="S2" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="T2" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -624,10 +622,8 @@
       <c r="A3" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26020746340576</t>
-        </is>
+      <c r="B3" t="n">
+        <v>26020746340576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -660,7 +656,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -684,10 +680,10 @@
         <v>290</v>
       </c>
       <c r="S3" t="n">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="T3" t="n">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
@@ -700,10 +696,8 @@
       <c r="A4" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>26020946668756</t>
-        </is>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -736,7 +730,7 @@
         <v>60</v>
       </c>
       <c r="K4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -760,10 +754,10 @@
         <v>161</v>
       </c>
       <c r="S4" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="T4" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -776,10 +770,8 @@
       <c r="A5" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>26022147703801</t>
-        </is>
+      <c r="B5" t="n">
+        <v>26022147703801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -812,7 +804,7 @@
         <v>60</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -836,10 +828,10 @@
         <v>322</v>
       </c>
       <c r="S5" t="n">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="T5" t="n">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -852,10 +844,8 @@
       <c r="A6" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>26022147748383</t>
-        </is>
+      <c r="B6" t="n">
+        <v>26022147748383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -888,7 +878,7 @@
         <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -912,10 +902,10 @@
         <v>130</v>
       </c>
       <c r="S6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="T6" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
@@ -928,10 +918,8 @@
       <c r="A7" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>26022347876463</t>
-        </is>
+      <c r="B7" t="n">
+        <v>26022347876463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -964,7 +952,7 @@
         <v>60</v>
       </c>
       <c r="K7" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -988,10 +976,10 @@
         <v>128</v>
       </c>
       <c r="S7" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="T7" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
@@ -1004,10 +992,8 @@
       <c r="A8" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>26022448136964</t>
-        </is>
+      <c r="B8" t="n">
+        <v>26022448136964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1040,7 +1026,7 @@
         <v>50</v>
       </c>
       <c r="K8" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1064,10 +1050,10 @@
         <v>162</v>
       </c>
       <c r="S8" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="T8" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -1080,10 +1066,8 @@
       <c r="A9" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>26022648266686</t>
-        </is>
+      <c r="B9" t="n">
+        <v>26022648266686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1112,7 +1096,7 @@
         <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1136,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1156,10 +1140,8 @@
       <c r="A10" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>26022648358294</t>
-        </is>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1192,7 +1174,7 @@
         <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1216,10 +1198,10 @@
         <v>65</v>
       </c>
       <c r="S10" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="T10" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
